--- a/System_Engineer_Roadmap_Tracker.xlsx
+++ b/System_Engineer_Roadmap_Tracker.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarmad Farooq\Documents\system-engineering-portfolio\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Weekly Plan" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Weekly Review" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Certifications" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Lab Log" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
+    <sheet name="Weekly Plan" sheetId="2" r:id="rId2"/>
+    <sheet name="Weekly Review" sheetId="3" r:id="rId3"/>
+    <sheet name="Certifications" sheetId="4" r:id="rId4"/>
+    <sheet name="Lab Log" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Plan'!$A$4:$I$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly Plan'!$A$4:$I$57</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="152511" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -29,473 +33,470 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
   <si>
-    <t xml:space="preserve">System Engineer Roadmap: Progress Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premier System | Red Hat + VMware | 4-month plan from trainee to client-ready engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: set to the date this plan was made. Change to your actual start date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks Completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Tasks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Completion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours Studied (Weekly Review)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Log Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certifications Passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progress by Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completion %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware Track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Hat Track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solutions &amp; Certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progress by Task Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Weekly Plan: change Status (dropdown) as you work. Blue cells are yours to edit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Weekly Review: log hours and a 1-5 self-score every Friday.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Lab Log: record each problem and fix; row 5 is an example to overwrite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Certifications: update status and score as you book and pass exams.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Yellow cell above (Start Date) drives Current Week and On track / Behind.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly Plan &amp; Checklist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set Status to Done as you finish each task. Everything on the Dashboard updates automatically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Command line, users, groups, permissions, ownership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">systemd services and package management (dnf/rpm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a RHEL VM with static IP and SSH hardening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LVM, file systems, mounting, RAID basics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create, extend and shrink LVM volumes in a lab VM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking: IP, DNS, firewalld, NIC bonding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datacenter networking: VLANs, trunks, LACP, MTU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configure VLAN and bond on RHEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash scripting basics: variables, loops, conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write a script that audits users, disk and services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardware &amp; Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization concepts: hypervisor, cluster, HA, live migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage: SAN vs NAS, iSCSI, Fibre Channel, RAID levels, IOPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE iLO and Dell iDRAC; firmware and RAID controllers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processors (Intel Xeon gens, AMD EPYC) and GPU servers (NVIDIA H200)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILESTONE: Month 1 review with mentor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware vSphere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESXi and vCenter installation (nested lab)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datastores, VM templates and cloning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtual networking: vSwitch, port groups, VLANs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clusters: HA, DRS, resource pools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vMotion: migrate a VM live between hosts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapshots, backups and restore basics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware vSAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vSAN architecture and storage policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build a vSAN cluster in the lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail a host or disk and observe vSAN behaviour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware NSX &amp; VCF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSX segments, gateways and distributed firewall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware Cloud Foundation (VCF) architecture overview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lifecycle Manager patching and monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILESTONE: Document full vSphere + vSAN lab build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Hat RHEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHCSA objectives: users, storage, SELinux, boot process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice RHCSA-style tasks under time limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, firewalld and SELinux troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Hat Ansible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ansible basics: inventory, ad-hoc commands, playbooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles, variables and templates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate a full server build with a playbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podman: images, containers, volumes, registries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes concepts: pods, deployments, services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run a multi-container application</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Hat OpenShift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpenShift architecture, projects, routes, storage, operators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deploy a small cluster or OpenShift Local and an app</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morpheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morpheus cloud management platform: overview and demo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILESTONE: App on OpenShift automated with Ansible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer decision path: containers + virtualization (Red Hat) vs virtualization only (VMware)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovery questions: workloads, growth, budget, skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sizing: CPU, RAM, storage (e.g. 50 TB to 75 TB SAN), licensing editions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External SAN, backup and DR design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE and Dell server and storage portfolio: what to quote when</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPU and AI workload basics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capstone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write BOM and architecture diagram for fictional customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write HLD (high-level design) document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build 10-slide solution presentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sit certification exam (RHCSA or VCP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Present capstone to manager / senior engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILESTONE: Final 4-month review and next 90-day plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task counts come from Weekly Plan. Fill in the blue cells at the end of each week (30 min with your mentor).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours Studied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-Score (1-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wins / Blockers / Next Week Goal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certification Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check vendor sites for current exam codes and prices; Broadcom/VMware has changed its program recently.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score / Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHCSA (EX200)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Hat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Week 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with timed labs in Week 9.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCP (VMware Certified Professional, current VCF/vSphere track)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware / Broadcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify exam code and prerequisites on Broadcom's site.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHCE / OpenShift Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stretch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Month 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan for the next 90 days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE / Dell partner training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE / Dell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ongoing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask Premier System about partner-portal access.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Log &amp; Runbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write down every issue you solve. This becomes your personal knowledge base. The first row is an example; overwrite it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problem / What I Did</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fix / Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHEL networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VM had no network after cloning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regenerated machine-id and fixed NIC name in nmcli</t>
+    <t>System Engineer Roadmap: Progress Dashboard</t>
+  </si>
+  <si>
+    <t>Premier System | Red Hat + VMware | 4-month plan from trainee to client-ready engineer</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Assumption: set to the date this plan was made. Change to your actual start date.</t>
+  </si>
+  <si>
+    <t>Planned End</t>
+  </si>
+  <si>
+    <t>Current Week</t>
+  </si>
+  <si>
+    <t>Time Elapsed</t>
+  </si>
+  <si>
+    <t>Tasks Completed</t>
+  </si>
+  <si>
+    <t>Total Tasks</t>
+  </si>
+  <si>
+    <t>Overall Completion</t>
+  </si>
+  <si>
+    <t>Schedule Status</t>
+  </si>
+  <si>
+    <t>Hours Studied (Weekly Review)</t>
+  </si>
+  <si>
+    <t>Lab Log Hours</t>
+  </si>
+  <si>
+    <t>Certifications Passed</t>
+  </si>
+  <si>
+    <t>Progress by Month</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Theme</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Completion %</t>
+  </si>
+  <si>
+    <t>Foundations</t>
+  </si>
+  <si>
+    <t>VMware Track</t>
+  </si>
+  <si>
+    <t>Red Hat Track</t>
+  </si>
+  <si>
+    <t>Solutions &amp; Certification</t>
+  </si>
+  <si>
+    <t>Progress by Task Type</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Theory</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t>Milestone</t>
+  </si>
+  <si>
+    <t>How to use</t>
+  </si>
+  <si>
+    <t>1. Weekly Plan: change Status (dropdown) as you work. Blue cells are yours to edit.</t>
+  </si>
+  <si>
+    <t>2. Weekly Review: log hours and a 1-5 self-score every Friday.</t>
+  </si>
+  <si>
+    <t>3. Lab Log: record each problem and fix; row 5 is an example to overwrite.</t>
+  </si>
+  <si>
+    <t>4. Certifications: update status and score as you book and pass exams.</t>
+  </si>
+  <si>
+    <t>5. Yellow cell above (Start Date) drives Current Week and On track / Behind.</t>
+  </si>
+  <si>
+    <t>Weekly Plan &amp; Checklist</t>
+  </si>
+  <si>
+    <t>Set Status to Done as you finish each task. Everything on the Dashboard updates automatically.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Track</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Date Done</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Linux Foundations</t>
+  </si>
+  <si>
+    <t>Command line, users, groups, permissions, ownership</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>systemd services and package management (dnf/rpm)</t>
+  </si>
+  <si>
+    <t>Build a RHEL VM with static IP and SSH hardening</t>
+  </si>
+  <si>
+    <t>LVM, file systems, mounting, RAID basics</t>
+  </si>
+  <si>
+    <t>Create, extend and shrink LVM volumes in a lab VM</t>
+  </si>
+  <si>
+    <t>Networking: IP, DNS, firewalld, NIC bonding</t>
+  </si>
+  <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>Datacenter networking: VLANs, trunks, LACP, MTU</t>
+  </si>
+  <si>
+    <t>Configure VLAN and bond on RHEL</t>
+  </si>
+  <si>
+    <t>Bash scripting basics: variables, loops, conditions</t>
+  </si>
+  <si>
+    <t>Write a script that audits users, disk and services</t>
+  </si>
+  <si>
+    <t>Hardware &amp; Storage</t>
+  </si>
+  <si>
+    <t>Virtualization concepts: hypervisor, cluster, HA, live migration</t>
+  </si>
+  <si>
+    <t>Storage: SAN vs NAS, iSCSI, Fibre Channel, RAID levels, IOPS</t>
+  </si>
+  <si>
+    <t>HPE iLO and Dell iDRAC; firmware and RAID controllers</t>
+  </si>
+  <si>
+    <t>Processors (Intel Xeon gens, AMD EPYC) and GPU servers (NVIDIA H200)</t>
+  </si>
+  <si>
+    <t>MILESTONE: Month 1 review with mentor</t>
+  </si>
+  <si>
+    <t>VMware vSphere</t>
+  </si>
+  <si>
+    <t>ESXi and vCenter installation (nested lab)</t>
+  </si>
+  <si>
+    <t>Datastores, VM templates and cloning</t>
+  </si>
+  <si>
+    <t>Virtual networking: vSwitch, port groups, VLANs</t>
+  </si>
+  <si>
+    <t>Clusters: HA, DRS, resource pools</t>
+  </si>
+  <si>
+    <t>vMotion: migrate a VM live between hosts</t>
+  </si>
+  <si>
+    <t>Snapshots, backups and restore basics</t>
+  </si>
+  <si>
+    <t>VMware vSAN</t>
+  </si>
+  <si>
+    <t>vSAN architecture and storage policies</t>
+  </si>
+  <si>
+    <t>Build a vSAN cluster in the lab</t>
+  </si>
+  <si>
+    <t>Fail a host or disk and observe vSAN behaviour</t>
+  </si>
+  <si>
+    <t>VMware NSX &amp; VCF</t>
+  </si>
+  <si>
+    <t>NSX segments, gateways and distributed firewall</t>
+  </si>
+  <si>
+    <t>VMware Cloud Foundation (VCF) architecture overview</t>
+  </si>
+  <si>
+    <t>Lifecycle Manager patching and monitoring</t>
+  </si>
+  <si>
+    <t>MILESTONE: Document full vSphere + vSAN lab build</t>
+  </si>
+  <si>
+    <t>Red Hat RHEL</t>
+  </si>
+  <si>
+    <t>RHCSA objectives: users, storage, SELinux, boot process</t>
+  </si>
+  <si>
+    <t>Practice RHCSA-style tasks under time limit</t>
+  </si>
+  <si>
+    <t>Networking, firewalld and SELinux troubleshooting</t>
+  </si>
+  <si>
+    <t>Red Hat Ansible</t>
+  </si>
+  <si>
+    <t>Ansible basics: inventory, ad-hoc commands, playbooks</t>
+  </si>
+  <si>
+    <t>Roles, variables and templates</t>
+  </si>
+  <si>
+    <t>Automate a full server build with a playbook</t>
+  </si>
+  <si>
+    <t>Containers</t>
+  </si>
+  <si>
+    <t>Podman: images, containers, volumes, registries</t>
+  </si>
+  <si>
+    <t>Kubernetes concepts: pods, deployments, services</t>
+  </si>
+  <si>
+    <t>Run a multi-container application</t>
+  </si>
+  <si>
+    <t>Red Hat OpenShift</t>
+  </si>
+  <si>
+    <t>OpenShift architecture, projects, routes, storage, operators</t>
+  </si>
+  <si>
+    <t>Deploy a small cluster or OpenShift Local and an app</t>
+  </si>
+  <si>
+    <t>Morpheus</t>
+  </si>
+  <si>
+    <t>Morpheus cloud management platform: overview and demo</t>
+  </si>
+  <si>
+    <t>MILESTONE: App on OpenShift automated with Ansible</t>
+  </si>
+  <si>
+    <t>Solution Design</t>
+  </si>
+  <si>
+    <t>Customer decision path: containers + virtualization (Red Hat) vs virtualization only (VMware)</t>
+  </si>
+  <si>
+    <t>Discovery questions: workloads, growth, budget, skills</t>
+  </si>
+  <si>
+    <t>Sizing: CPU, RAM, storage (e.g. 50 TB to 75 TB SAN), licensing editions</t>
+  </si>
+  <si>
+    <t>External SAN, backup and DR design</t>
+  </si>
+  <si>
+    <t>HPE and Dell server and storage portfolio: what to quote when</t>
+  </si>
+  <si>
+    <t>GPU and AI workload basics</t>
+  </si>
+  <si>
+    <t>Capstone</t>
+  </si>
+  <si>
+    <t>Write BOM and architecture diagram for fictional customer</t>
+  </si>
+  <si>
+    <t>Write HLD (high-level design) document</t>
+  </si>
+  <si>
+    <t>Build 10-slide solution presentation</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>Sit certification exam (RHCSA or VCP)</t>
+  </si>
+  <si>
+    <t>Present capstone to manager / senior engineer</t>
+  </si>
+  <si>
+    <t>MILESTONE: Final 4-month review and next 90-day plan</t>
+  </si>
+  <si>
+    <t>Weekly Review</t>
+  </si>
+  <si>
+    <t>Task counts come from Weekly Plan. Fill in the blue cells at the end of each week (30 min with your mentor).</t>
+  </si>
+  <si>
+    <t>Hours Studied</t>
+  </si>
+  <si>
+    <t>Self-Score (1-5)</t>
+  </si>
+  <si>
+    <t>Wins / Blockers / Next Week Goal</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Certification Tracker</t>
+  </si>
+  <si>
+    <t>Check vendor sites for current exam codes and prices; Broadcom/VMware has changed its program recently.</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Target Date</t>
+  </si>
+  <si>
+    <t>Score / Result</t>
+  </si>
+  <si>
+    <t>RHCSA (EX200)</t>
+  </si>
+  <si>
+    <t>Red Hat</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Week 16</t>
+  </si>
+  <si>
+    <t>Practice with timed labs in Week 9.</t>
+  </si>
+  <si>
+    <t>VCP (VMware Certified Professional, current VCF/vSphere track)</t>
+  </si>
+  <si>
+    <t>VMware / Broadcom</t>
+  </si>
+  <si>
+    <t>Verify exam code and prerequisites on Broadcom's site.</t>
+  </si>
+  <si>
+    <t>RHCE / OpenShift Administration</t>
+  </si>
+  <si>
+    <t>Stretch</t>
+  </si>
+  <si>
+    <t>After Month 4</t>
+  </si>
+  <si>
+    <t>Plan for the next 90 days.</t>
+  </si>
+  <si>
+    <t>HPE / Dell partner training</t>
+  </si>
+  <si>
+    <t>HPE / Dell</t>
+  </si>
+  <si>
+    <t>Supporting</t>
+  </si>
+  <si>
+    <t>Ongoing</t>
+  </si>
+  <si>
+    <t>Ask Premier System about partner-portal access.</t>
+  </si>
+  <si>
+    <t>Lab Log &amp; Runbook</t>
+  </si>
+  <si>
+    <t>Write down every issue you solve. This becomes your personal knowledge base. The first row is an example; overwrite it.</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Problem / What I Did</t>
+  </si>
+  <si>
+    <t>Fix / Learning</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>RHEL networking</t>
+  </si>
+  <si>
+    <t>VM had no network after cloning</t>
+  </si>
+  <si>
+    <t>Regenerated machine-id and fixed NIC name in nmcli</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;Week &quot;0"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
-    <numFmt numFmtId="168" formatCode="General"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="&quot;Month &quot;0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;Week &quot;0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="&quot;Month &quot;0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,92 +505,56 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -619,14 +584,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -642,177 +607,131 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="32">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
+        <b/>
+        <color rgb="FF1F3864"/>
         <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
+        <name val="Arial"/>
       </font>
       <fill>
         <patternFill>
@@ -822,11 +741,9 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <color rgb="FF9C0006"/>
         <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
@@ -835,50 +752,10 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F3864"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDDEBF7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
+        <b/>
+        <color rgb="FF006100"/>
         <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
@@ -886,41 +763,8 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF1F3864"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -979,15 +823,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -996,7 +858,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1004,7 +866,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1015,6 +877,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1025,6 +888,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1034,7 +898,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!E18</c:f>
+              <c:f>Dashboard!$E$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1045,29 +909,37 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="f9f9f9"/>
+                <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -1076,33 +948,36 @@
             <c:showCatName val="1"/>
             <c:showSerName val="1"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Dashboard!$A$19:$A$22</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>"Month "0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Month 1</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Month 2</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Month 3</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Month 4</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1126,13 +1001,20 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="6102153"/>
-        <c:axId val="83198563"/>
+        <c:axId val="-608974928"/>
+        <c:axId val="-608976016"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6102153"/>
+        <c:axId val="-608974928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1155,16 +1037,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83198563"/>
+        <c:crossAx val="-608976016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1172,7 +1055,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83198563"/>
+        <c:axId val="-608976016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1207,16 +1090,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6102153"/>
+        <c:crossAx val="-608974928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1229,25 +1113,33 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1256,7 +1148,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1264,7 +1156,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1275,6 +1167,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1285,6 +1178,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1294,7 +1188,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Weekly Review'!E4</c:f>
+              <c:f>'Weekly Review'!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1305,26 +1199,34 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="f9f9f9"/>
+                <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1332,8 +1234,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1341,60 +1244,61 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Weekly Review'!$A$5:$A$20</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>"Week "0</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>Week 1</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Week 2</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Week 3</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Week 4</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Week 5</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Week 6</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Week 7</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Week 8</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Week 9</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Week 10</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Week 11</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Week 12</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Week 13</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Week 14</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Week 15</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Week 16</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1454,13 +1358,20 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="87548258"/>
-        <c:axId val="47136292"/>
+        <c:axId val="-608981456"/>
+        <c:axId val="-608977104"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="87548258"/>
+        <c:axId val="-608981456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1483,16 +1394,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47136292"/>
+        <c:crossAx val="-608977104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1500,7 +1412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47136292"/>
+        <c:axId val="-608977104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1535,16 +1447,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87548258"/>
+        <c:crossAx val="-608981456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1557,25 +1470,33 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1584,7 +1505,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1592,7 +1513,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1613,6 +1534,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1622,7 +1544,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Weekly Review'!F4</c:f>
+              <c:f>'Weekly Review'!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1633,26 +1555,34 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="f9f9f9"/>
+                <a:srgbClr val="F9F9F9"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1660,8 +1590,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1669,78 +1600,86 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Weekly Review'!$A$5:$A$20</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>"Week "0</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>Week 1</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Week 2</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Week 3</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Week 4</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Week 5</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Week 6</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Week 7</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Week 8</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Week 9</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Week 10</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Week 11</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Week 12</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Week 13</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Week 14</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Week 15</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Week 16</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Weekly Review'!$F$5:$F$20</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="16"/>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="47140834"/>
-        <c:axId val="37493363"/>
+        <c:axId val="-608980912"/>
+        <c:axId val="-608967856"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="47140834"/>
+        <c:axId val="-608980912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1763,16 +1702,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37493363"/>
+        <c:crossAx val="-608967856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1780,7 +1720,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37493363"/>
+        <c:axId val="-608967856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1796,7 +1736,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1813,16 +1753,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47140834"/>
+        <c:crossAx val="-608980912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1835,23 +1776,29 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -1865,14 +1812,14 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>163800</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7095960" y="571680"/>
-        <a:ext cx="5039640" cy="2699640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1895,14 +1842,14 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>163440</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7095960" y="3619440"/>
-        <a:ext cx="7919640" cy="2699640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1925,14 +1872,14 @@
       <xdr:row>48</xdr:row>
       <xdr:rowOff>163440</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7095960" y="6667560"/>
-        <a:ext cx="7919640" cy="2699640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1945,46 +1892,42 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1992,12 +1935,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -2026,7 +1969,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2047,7 +1990,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -2098,7 +2041,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2116,145 +2059,144 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>46302</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <f aca="false">B4+112</f>
+      <c r="B5" s="6">
+        <f>B4+112</f>
         <v>46414</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <f aca="true">MAX(1,MIN(16,INT((TODAY()-B4)/7)+1))</f>
+      <c r="B6" s="7">
+        <f ca="1">MAX(1,MIN(16,INT((TODAY()-B4)/7)+1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <f aca="true">MIN(1,MAX(0,(TODAY()-B4)/112))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="8">
+        <f ca="1">MIN(1,MAX(0,(TODAY()-B4)/112))</f>
+        <v>1.7857142857142856E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!G5:G57,"Done")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="9">
+        <f>COUNTIF('Weekly Plan'!G5:G57,"Done")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="n">
-        <f aca="false">COUNTA('Weekly Plan'!E5:E57)</f>
+      <c r="B9" s="9">
+        <f>COUNTA('Weekly Plan'!E5:E57)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="n">
-        <f aca="false">IF(B9=0,0,B8/B9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="10">
+        <f>IF(B9=0,0,B8/B9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="str">
-        <f aca="false">IF(B10&gt;=B7,"On track","Behind schedule")</f>
-        <v>On track</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f ca="1">IF(B10&gt;=B7,"On track","Behind schedule")</f>
+        <v>Behind schedule</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="n">
-        <f aca="false">'Weekly Review'!F21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12">
+        <f>'Weekly Review'!F21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="n">
-        <f aca="false">SUM('Lab Log'!F5:F105)</f>
+      <c r="B13" s="12">
+        <f>SUM('Lab Log'!F5:F105)</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">COUNTIF(Certifications!E5:E8,"Passed")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="9">
+        <f>COUNTIF(Certifications!E5:E8,"Passed")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>15</v>
       </c>
@@ -2271,92 +2213,92 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="n">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
         <v>1</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$B$5:$B$57,A19)</f>
+      <c r="C19" s="9">
+        <f>COUNTIF('Weekly Plan'!$B$5:$B$57,A19)</f>
         <v>15</v>
       </c>
-      <c r="D19" s="9" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$B$5:$B$57,A19,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <f aca="false">IF(C19=0,0,D19/C19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="n">
+      <c r="D19" s="9">
+        <f>COUNTIFS('Weekly Plan'!$B$5:$B$57,A19,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <f>IF(C19=0,0,D19/C19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$B$5:$B$57,A20)</f>
+      <c r="C20" s="9">
+        <f>COUNTIF('Weekly Plan'!$B$5:$B$57,A20)</f>
         <v>13</v>
       </c>
-      <c r="D20" s="9" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$B$5:$B$57,A20,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <f aca="false">IF(C20=0,0,D20/C20)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="n">
+      <c r="D20" s="9">
+        <f>COUNTIFS('Weekly Plan'!$B$5:$B$57,A20,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="8">
+        <f>IF(C20=0,0,D20/C20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
         <v>3</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$B$5:$B$57,A21)</f>
+      <c r="C21" s="9">
+        <f>COUNTIF('Weekly Plan'!$B$5:$B$57,A21)</f>
         <v>13</v>
       </c>
-      <c r="D21" s="9" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$B$5:$B$57,A21,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <f aca="false">IF(C21=0,0,D21/C21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="n">
+      <c r="D21" s="9">
+        <f>COUNTIFS('Weekly Plan'!$B$5:$B$57,A21,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <f>IF(C21=0,0,D21/C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$B$5:$B$57,A22)</f>
+      <c r="C22" s="9">
+        <f>COUNTIF('Weekly Plan'!$B$5:$B$57,A22)</f>
         <v>12</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$B$5:$B$57,A22,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <f aca="false">IF(C22=0,0,D22/C22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="9">
+        <f>COUNTIFS('Weekly Plan'!$B$5:$B$57,A22,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <f>IF(C22=0,0,D22/C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>25</v>
       </c>
@@ -2371,138 +2313,130 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="9"/>
-      <c r="C27" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$F$5:$F$57,A27)</f>
+      <c r="C27" s="9">
+        <f>COUNTIF('Weekly Plan'!$F$5:$F$57,A27)</f>
         <v>26</v>
       </c>
-      <c r="D27" s="9" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$F$5:$F$57,A27,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <f aca="false">IF(C27=0,0,D27/C27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="9">
+        <f>COUNTIFS('Weekly Plan'!$F$5:$F$57,A27,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <f>IF(C27=0,0,D27/C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$F$5:$F$57,A28)</f>
+      <c r="C28" s="9">
+        <f>COUNTIF('Weekly Plan'!$F$5:$F$57,A28)</f>
         <v>21</v>
       </c>
-      <c r="D28" s="9" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$F$5:$F$57,A28,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <f aca="false">IF(C28=0,0,D28/C28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="9">
+        <f>COUNTIFS('Weekly Plan'!$F$5:$F$57,A28,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <f>IF(C28=0,0,D28/C28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="9"/>
-      <c r="C29" s="9" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$F$5:$F$57,A29)</f>
+      <c r="C29" s="9">
+        <f>COUNTIF('Weekly Plan'!$F$5:$F$57,A29)</f>
         <v>6</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$F$5:$F$57,A29,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <f aca="false">IF(C29=0,0,D29/C29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="9">
+        <f>COUNTIFS('Weekly Plan'!$F$5:$F$57,A29,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <f>IF(C29=0,0,D29/C29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"On track"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"Behind schedule"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I57"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="62" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>37</v>
       </c>
@@ -2531,14 +2465,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="n">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="18">
         <v>1</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="19">
         <v>1</v>
       </c>
       <c r="D5" s="20" t="s">
@@ -2556,14 +2490,14 @@
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="18">
         <v>1</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="19">
         <v>1</v>
       </c>
       <c r="D6" s="20" t="s">
@@ -2581,14 +2515,14 @@
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="n">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="18">
         <v>1</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="19">
         <v>1</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -2606,14 +2540,14 @@
       <c r="H7" s="22"/>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="n">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="18">
         <v>1</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="19">
         <v>2</v>
       </c>
       <c r="D8" s="20" t="s">
@@ -2631,14 +2565,14 @@
       <c r="H8" s="22"/>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="n">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="18">
         <v>1</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="19">
         <v>2</v>
       </c>
       <c r="D9" s="20" t="s">
@@ -2656,14 +2590,14 @@
       <c r="H9" s="22"/>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="n">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="18">
         <v>1</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="19">
         <v>2</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -2681,14 +2615,14 @@
       <c r="H10" s="22"/>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="n">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="18">
         <v>1</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="19">
         <v>3</v>
       </c>
       <c r="D11" s="20" t="s">
@@ -2706,14 +2640,14 @@
       <c r="H11" s="22"/>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="n">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="18">
         <v>1</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="19">
         <v>3</v>
       </c>
       <c r="D12" s="20" t="s">
@@ -2731,14 +2665,14 @@
       <c r="H12" s="22"/>
       <c r="I12" s="23"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="n">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="18">
         <v>1</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="19">
         <v>3</v>
       </c>
       <c r="D13" s="20" t="s">
@@ -2756,14 +2690,14 @@
       <c r="H13" s="22"/>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="n">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="18">
         <v>1</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="19">
         <v>3</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -2781,14 +2715,14 @@
       <c r="H14" s="22"/>
       <c r="I14" s="23"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="n">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="18">
         <v>1</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="19">
         <v>4</v>
       </c>
       <c r="D15" s="20" t="s">
@@ -2806,14 +2740,14 @@
       <c r="H15" s="22"/>
       <c r="I15" s="23"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="n">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="18">
         <v>1</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="19">
         <v>4</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -2831,14 +2765,14 @@
       <c r="H16" s="22"/>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="n">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>13</v>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="18">
         <v>1</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="19">
         <v>4</v>
       </c>
       <c r="D17" s="20" t="s">
@@ -2856,14 +2790,14 @@
       <c r="H17" s="22"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="n">
+    <row r="18" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="18">
         <v>1</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="19">
         <v>4</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -2881,14 +2815,14 @@
       <c r="H18" s="22"/>
       <c r="I18" s="23"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="n">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
         <v>15</v>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="18">
         <v>1</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="19">
         <v>4</v>
       </c>
       <c r="D19" s="20" t="s">
@@ -2906,14 +2840,14 @@
       <c r="H19" s="22"/>
       <c r="I19" s="23"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="n">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="18">
         <v>2</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="19">
         <v>5</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -2931,14 +2865,14 @@
       <c r="H20" s="22"/>
       <c r="I20" s="23"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="n">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
         <v>17</v>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="18">
         <v>2</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="19">
         <v>5</v>
       </c>
       <c r="D21" s="20" t="s">
@@ -2956,14 +2890,14 @@
       <c r="H21" s="22"/>
       <c r="I21" s="23"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="n">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="18">
         <v>2</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="19">
         <v>5</v>
       </c>
       <c r="D22" s="20" t="s">
@@ -2981,14 +2915,14 @@
       <c r="H22" s="22"/>
       <c r="I22" s="23"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="n">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
         <v>19</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="18">
         <v>2</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="19">
         <v>6</v>
       </c>
       <c r="D23" s="20" t="s">
@@ -3006,14 +2940,14 @@
       <c r="H23" s="22"/>
       <c r="I23" s="23"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="n">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>20</v>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="18">
         <v>2</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="19">
         <v>6</v>
       </c>
       <c r="D24" s="20" t="s">
@@ -3031,14 +2965,14 @@
       <c r="H24" s="22"/>
       <c r="I24" s="23"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="n">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
         <v>21</v>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="18">
         <v>2</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="19">
         <v>6</v>
       </c>
       <c r="D25" s="20" t="s">
@@ -3056,14 +2990,14 @@
       <c r="H25" s="22"/>
       <c r="I25" s="23"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="n">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
         <v>22</v>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="18">
         <v>2</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="19">
         <v>7</v>
       </c>
       <c r="D26" s="20" t="s">
@@ -3081,14 +3015,14 @@
       <c r="H26" s="22"/>
       <c r="I26" s="23"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="n">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
         <v>23</v>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="18">
         <v>2</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="19">
         <v>7</v>
       </c>
       <c r="D27" s="20" t="s">
@@ -3106,14 +3040,14 @@
       <c r="H27" s="22"/>
       <c r="I27" s="23"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="n">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
         <v>24</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="18">
         <v>2</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="19">
         <v>7</v>
       </c>
       <c r="D28" s="20" t="s">
@@ -3131,14 +3065,14 @@
       <c r="H28" s="22"/>
       <c r="I28" s="23"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="n">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
         <v>25</v>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="18">
         <v>2</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C29" s="19">
         <v>8</v>
       </c>
       <c r="D29" s="20" t="s">
@@ -3156,14 +3090,14 @@
       <c r="H29" s="22"/>
       <c r="I29" s="23"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="n">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
         <v>26</v>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="18">
         <v>2</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="19">
         <v>8</v>
       </c>
       <c r="D30" s="20" t="s">
@@ -3181,14 +3115,14 @@
       <c r="H30" s="22"/>
       <c r="I30" s="23"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="n">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
         <v>27</v>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="18">
         <v>2</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="19">
         <v>8</v>
       </c>
       <c r="D31" s="20" t="s">
@@ -3206,14 +3140,14 @@
       <c r="H31" s="22"/>
       <c r="I31" s="23"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="n">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="17">
         <v>28</v>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="18">
         <v>2</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="19">
         <v>8</v>
       </c>
       <c r="D32" s="20" t="s">
@@ -3231,14 +3165,14 @@
       <c r="H32" s="22"/>
       <c r="I32" s="23"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="n">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="17">
         <v>29</v>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="18">
         <v>3</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="19">
         <v>9</v>
       </c>
       <c r="D33" s="20" t="s">
@@ -3256,14 +3190,14 @@
       <c r="H33" s="22"/>
       <c r="I33" s="23"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="n">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
         <v>30</v>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="18">
         <v>3</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="19">
         <v>9</v>
       </c>
       <c r="D34" s="20" t="s">
@@ -3281,14 +3215,14 @@
       <c r="H34" s="22"/>
       <c r="I34" s="23"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="n">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="17">
         <v>31</v>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="18">
         <v>3</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C35" s="19">
         <v>9</v>
       </c>
       <c r="D35" s="20" t="s">
@@ -3306,14 +3240,14 @@
       <c r="H35" s="22"/>
       <c r="I35" s="23"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="n">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="17">
         <v>32</v>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="18">
         <v>3</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="19">
         <v>10</v>
       </c>
       <c r="D36" s="20" t="s">
@@ -3331,14 +3265,14 @@
       <c r="H36" s="22"/>
       <c r="I36" s="23"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="n">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="17">
         <v>33</v>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="18">
         <v>3</v>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="19">
         <v>10</v>
       </c>
       <c r="D37" s="20" t="s">
@@ -3356,14 +3290,14 @@
       <c r="H37" s="22"/>
       <c r="I37" s="23"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="n">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="17">
         <v>34</v>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="18">
         <v>3</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="19">
         <v>10</v>
       </c>
       <c r="D38" s="20" t="s">
@@ -3381,14 +3315,14 @@
       <c r="H38" s="22"/>
       <c r="I38" s="23"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="n">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="17">
         <v>35</v>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="18">
         <v>3</v>
       </c>
-      <c r="C39" s="19" t="n">
+      <c r="C39" s="19">
         <v>11</v>
       </c>
       <c r="D39" s="20" t="s">
@@ -3406,14 +3340,14 @@
       <c r="H39" s="22"/>
       <c r="I39" s="23"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="n">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="17">
         <v>36</v>
       </c>
-      <c r="B40" s="18" t="n">
+      <c r="B40" s="18">
         <v>3</v>
       </c>
-      <c r="C40" s="19" t="n">
+      <c r="C40" s="19">
         <v>11</v>
       </c>
       <c r="D40" s="20" t="s">
@@ -3431,14 +3365,14 @@
       <c r="H40" s="22"/>
       <c r="I40" s="23"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="n">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="17">
         <v>37</v>
       </c>
-      <c r="B41" s="18" t="n">
+      <c r="B41" s="18">
         <v>3</v>
       </c>
-      <c r="C41" s="19" t="n">
+      <c r="C41" s="19">
         <v>11</v>
       </c>
       <c r="D41" s="20" t="s">
@@ -3456,14 +3390,14 @@
       <c r="H41" s="22"/>
       <c r="I41" s="23"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="n">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="17">
         <v>38</v>
       </c>
-      <c r="B42" s="18" t="n">
+      <c r="B42" s="18">
         <v>3</v>
       </c>
-      <c r="C42" s="19" t="n">
+      <c r="C42" s="19">
         <v>12</v>
       </c>
       <c r="D42" s="20" t="s">
@@ -3481,14 +3415,14 @@
       <c r="H42" s="22"/>
       <c r="I42" s="23"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="n">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="17">
         <v>39</v>
       </c>
-      <c r="B43" s="18" t="n">
+      <c r="B43" s="18">
         <v>3</v>
       </c>
-      <c r="C43" s="19" t="n">
+      <c r="C43" s="19">
         <v>12</v>
       </c>
       <c r="D43" s="20" t="s">
@@ -3506,14 +3440,14 @@
       <c r="H43" s="22"/>
       <c r="I43" s="23"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17" t="n">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
         <v>40</v>
       </c>
-      <c r="B44" s="18" t="n">
+      <c r="B44" s="18">
         <v>3</v>
       </c>
-      <c r="C44" s="19" t="n">
+      <c r="C44" s="19">
         <v>12</v>
       </c>
       <c r="D44" s="20" t="s">
@@ -3531,14 +3465,14 @@
       <c r="H44" s="22"/>
       <c r="I44" s="23"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="n">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="17">
         <v>41</v>
       </c>
-      <c r="B45" s="18" t="n">
+      <c r="B45" s="18">
         <v>3</v>
       </c>
-      <c r="C45" s="19" t="n">
+      <c r="C45" s="19">
         <v>12</v>
       </c>
       <c r="D45" s="20" t="s">
@@ -3556,14 +3490,14 @@
       <c r="H45" s="22"/>
       <c r="I45" s="23"/>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="17" t="n">
+    <row r="46" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="17">
         <v>42</v>
       </c>
-      <c r="B46" s="18" t="n">
+      <c r="B46" s="18">
         <v>4</v>
       </c>
-      <c r="C46" s="19" t="n">
+      <c r="C46" s="19">
         <v>13</v>
       </c>
       <c r="D46" s="20" t="s">
@@ -3581,14 +3515,14 @@
       <c r="H46" s="22"/>
       <c r="I46" s="23"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="n">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="17">
         <v>43</v>
       </c>
-      <c r="B47" s="18" t="n">
+      <c r="B47" s="18">
         <v>4</v>
       </c>
-      <c r="C47" s="19" t="n">
+      <c r="C47" s="19">
         <v>13</v>
       </c>
       <c r="D47" s="20" t="s">
@@ -3606,14 +3540,14 @@
       <c r="H47" s="22"/>
       <c r="I47" s="23"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17" t="n">
+    <row r="48" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="17">
         <v>44</v>
       </c>
-      <c r="B48" s="18" t="n">
+      <c r="B48" s="18">
         <v>4</v>
       </c>
-      <c r="C48" s="19" t="n">
+      <c r="C48" s="19">
         <v>13</v>
       </c>
       <c r="D48" s="20" t="s">
@@ -3631,14 +3565,14 @@
       <c r="H48" s="22"/>
       <c r="I48" s="23"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="n">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
         <v>45</v>
       </c>
-      <c r="B49" s="18" t="n">
+      <c r="B49" s="18">
         <v>4</v>
       </c>
-      <c r="C49" s="19" t="n">
+      <c r="C49" s="19">
         <v>14</v>
       </c>
       <c r="D49" s="20" t="s">
@@ -3656,14 +3590,14 @@
       <c r="H49" s="22"/>
       <c r="I49" s="23"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="18" t="n">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
+        <v>46</v>
+      </c>
+      <c r="B50" s="18">
         <v>4</v>
       </c>
-      <c r="C50" s="19" t="n">
+      <c r="C50" s="19">
         <v>14</v>
       </c>
       <c r="D50" s="20" t="s">
@@ -3681,14 +3615,14 @@
       <c r="H50" s="22"/>
       <c r="I50" s="23"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="n">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
         <v>47</v>
       </c>
-      <c r="B51" s="18" t="n">
+      <c r="B51" s="18">
         <v>4</v>
       </c>
-      <c r="C51" s="19" t="n">
+      <c r="C51" s="19">
         <v>14</v>
       </c>
       <c r="D51" s="20" t="s">
@@ -3706,14 +3640,14 @@
       <c r="H51" s="22"/>
       <c r="I51" s="23"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="n">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
         <v>48</v>
       </c>
-      <c r="B52" s="18" t="n">
+      <c r="B52" s="18">
         <v>4</v>
       </c>
-      <c r="C52" s="19" t="n">
+      <c r="C52" s="19">
         <v>15</v>
       </c>
       <c r="D52" s="20" t="s">
@@ -3731,14 +3665,14 @@
       <c r="H52" s="22"/>
       <c r="I52" s="23"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17" t="n">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="17">
         <v>49</v>
       </c>
-      <c r="B53" s="18" t="n">
+      <c r="B53" s="18">
         <v>4</v>
       </c>
-      <c r="C53" s="19" t="n">
+      <c r="C53" s="19">
         <v>15</v>
       </c>
       <c r="D53" s="20" t="s">
@@ -3756,14 +3690,14 @@
       <c r="H53" s="22"/>
       <c r="I53" s="23"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="n">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="17">
         <v>50</v>
       </c>
-      <c r="B54" s="18" t="n">
+      <c r="B54" s="18">
         <v>4</v>
       </c>
-      <c r="C54" s="19" t="n">
+      <c r="C54" s="19">
         <v>15</v>
       </c>
       <c r="D54" s="20" t="s">
@@ -3781,14 +3715,14 @@
       <c r="H54" s="22"/>
       <c r="I54" s="23"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="n">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="17">
         <v>51</v>
       </c>
-      <c r="B55" s="18" t="n">
+      <c r="B55" s="18">
         <v>4</v>
       </c>
-      <c r="C55" s="19" t="n">
+      <c r="C55" s="19">
         <v>16</v>
       </c>
       <c r="D55" s="20" t="s">
@@ -3806,14 +3740,14 @@
       <c r="H55" s="22"/>
       <c r="I55" s="23"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17" t="n">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="17">
         <v>52</v>
       </c>
-      <c r="B56" s="18" t="n">
+      <c r="B56" s="18">
         <v>4</v>
       </c>
-      <c r="C56" s="19" t="n">
+      <c r="C56" s="19">
         <v>16</v>
       </c>
       <c r="D56" s="20" t="s">
@@ -3831,14 +3765,14 @@
       <c r="H56" s="22"/>
       <c r="I56" s="23"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17" t="n">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="17">
         <v>53</v>
       </c>
-      <c r="B57" s="18" t="n">
+      <c r="B57" s="18">
         <v>4</v>
       </c>
-      <c r="C57" s="19" t="n">
+      <c r="C57" s="19">
         <v>16</v>
       </c>
       <c r="D57" s="20" t="s">
@@ -3859,61 +3793,52 @@
   </sheetData>
   <autoFilter ref="A4:I57"/>
   <conditionalFormatting sqref="G5:G57">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:F57">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$F5="Milestone"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G57" type="list">
+    <dataValidation type="list" sqref="G5:G57">
       <formula1>"Not Started,In Progress,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="60"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="9" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>38</v>
       </c>
@@ -3939,458 +3864,450 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="n">
-        <f aca="false">INT((1-1)/4)+1</f>
+      <c r="B5" s="18">
+        <f>INT((1-1)/4)+1</f>
         <v>1</v>
       </c>
-      <c r="C5" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A5)</f>
+      <c r="C5" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A5)</f>
         <v>3</v>
       </c>
-      <c r="D5" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A5,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="25" t="n">
-        <f aca="false">IF(C5=0,0,D5/C5)</f>
+      <c r="D5" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A5,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="25">
+        <f t="shared" ref="E5:E21" si="0">IF(C5=0,0,D5/C5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="21"/>
       <c r="H5" s="23"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="n">
-        <f aca="false">INT((2-1)/4)+1</f>
+      <c r="B6" s="18">
+        <f>INT((2-1)/4)+1</f>
         <v>1</v>
       </c>
-      <c r="C6" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A6)</f>
+      <c r="C6" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A6)</f>
         <v>3</v>
       </c>
-      <c r="D6" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A6,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <f aca="false">IF(C6=0,0,D6/C6)</f>
+      <c r="D6" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A6,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="21"/>
       <c r="H6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="n">
-        <f aca="false">INT((3-1)/4)+1</f>
+      <c r="B7" s="18">
+        <f>INT((3-1)/4)+1</f>
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A7)</f>
+      <c r="C7" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A7)</f>
         <v>4</v>
       </c>
-      <c r="D7" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A7,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="25" t="n">
-        <f aca="false">IF(C7=0,0,D7/C7)</f>
+      <c r="D7" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A7,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="21"/>
       <c r="H7" s="23"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="n">
-        <f aca="false">INT((4-1)/4)+1</f>
+      <c r="B8" s="18">
+        <f>INT((4-1)/4)+1</f>
         <v>1</v>
       </c>
-      <c r="C8" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A8)</f>
+      <c r="C8" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A8)</f>
         <v>5</v>
       </c>
-      <c r="D8" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A8,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <f aca="false">IF(C8=0,0,D8/C8)</f>
+      <c r="D8" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A8,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="21"/>
       <c r="H8" s="23"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="n">
-        <f aca="false">INT((5-1)/4)+1</f>
+      <c r="B9" s="18">
+        <f>INT((5-1)/4)+1</f>
         <v>2</v>
       </c>
-      <c r="C9" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A9)</f>
+      <c r="C9" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A9)</f>
         <v>3</v>
       </c>
-      <c r="D9" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A9,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <f aca="false">IF(C9=0,0,D9/C9)</f>
+      <c r="D9" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A9,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="21"/>
       <c r="H9" s="23"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="n">
-        <f aca="false">INT((6-1)/4)+1</f>
+      <c r="B10" s="18">
+        <f>INT((6-1)/4)+1</f>
         <v>2</v>
       </c>
-      <c r="C10" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A10)</f>
+      <c r="C10" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A10)</f>
         <v>3</v>
       </c>
-      <c r="D10" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A10,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <f aca="false">IF(C10=0,0,D10/C10)</f>
+      <c r="D10" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A10,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="21"/>
       <c r="H10" s="23"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="n">
-        <f aca="false">INT((7-1)/4)+1</f>
+      <c r="B11" s="18">
+        <f>INT((7-1)/4)+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A11)</f>
+      <c r="C11" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A11)</f>
         <v>3</v>
       </c>
-      <c r="D11" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A11,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="n">
-        <f aca="false">IF(C11=0,0,D11/C11)</f>
+      <c r="D11" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A11,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="21"/>
       <c r="H11" s="23"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="n">
-        <f aca="false">INT((8-1)/4)+1</f>
+      <c r="B12" s="18">
+        <f>INT((8-1)/4)+1</f>
         <v>2</v>
       </c>
-      <c r="C12" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A12)</f>
+      <c r="C12" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A12)</f>
         <v>4</v>
       </c>
-      <c r="D12" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A12,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="n">
-        <f aca="false">IF(C12=0,0,D12/C12)</f>
+      <c r="D12" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A12,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="21"/>
       <c r="H12" s="23"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="n">
-        <f aca="false">INT((9-1)/4)+1</f>
+      <c r="B13" s="18">
+        <f>INT((9-1)/4)+1</f>
         <v>3</v>
       </c>
-      <c r="C13" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A13)</f>
+      <c r="C13" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A13)</f>
         <v>3</v>
       </c>
-      <c r="D13" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A13,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="n">
-        <f aca="false">IF(C13=0,0,D13/C13)</f>
+      <c r="D13" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A13,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="21"/>
       <c r="H13" s="23"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="n">
-        <f aca="false">INT((10-1)/4)+1</f>
+      <c r="B14" s="18">
+        <f>INT((10-1)/4)+1</f>
         <v>3</v>
       </c>
-      <c r="C14" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A14)</f>
+      <c r="C14" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A14)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A14,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="25" t="n">
-        <f aca="false">IF(C14=0,0,D14/C14)</f>
+      <c r="D14" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A14,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="21"/>
       <c r="H14" s="23"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="n">
-        <f aca="false">INT((11-1)/4)+1</f>
+      <c r="B15" s="18">
+        <f>INT((11-1)/4)+1</f>
         <v>3</v>
       </c>
-      <c r="C15" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A15)</f>
+      <c r="C15" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A15)</f>
         <v>3</v>
       </c>
-      <c r="D15" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A15,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="25" t="n">
-        <f aca="false">IF(C15=0,0,D15/C15)</f>
+      <c r="D15" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A15,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="21"/>
       <c r="H15" s="23"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="n">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="n">
-        <f aca="false">INT((12-1)/4)+1</f>
+      <c r="B16" s="18">
+        <f>INT((12-1)/4)+1</f>
         <v>3</v>
       </c>
-      <c r="C16" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A16)</f>
+      <c r="C16" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A16)</f>
         <v>4</v>
       </c>
-      <c r="D16" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A16,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <f aca="false">IF(C16=0,0,D16/C16)</f>
+      <c r="D16" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A16,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="21"/>
       <c r="H16" s="23"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="n">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
         <v>13</v>
       </c>
-      <c r="B17" s="18" t="n">
-        <f aca="false">INT((13-1)/4)+1</f>
+      <c r="B17" s="18">
+        <f>INT((13-1)/4)+1</f>
         <v>4</v>
       </c>
-      <c r="C17" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A17)</f>
+      <c r="C17" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A17)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A17,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="25" t="n">
-        <f aca="false">IF(C17=0,0,D17/C17)</f>
+      <c r="D17" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A17,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="21"/>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="n">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="n">
-        <f aca="false">INT((14-1)/4)+1</f>
+      <c r="B18" s="18">
+        <f>INT((14-1)/4)+1</f>
         <v>4</v>
       </c>
-      <c r="C18" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A18)</f>
+      <c r="C18" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A18)</f>
         <v>3</v>
       </c>
-      <c r="D18" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A18,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <f aca="false">IF(C18=0,0,D18/C18)</f>
+      <c r="D18" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A18,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="21"/>
       <c r="H18" s="23"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="n">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>15</v>
       </c>
-      <c r="B19" s="18" t="n">
-        <f aca="false">INT((15-1)/4)+1</f>
+      <c r="B19" s="18">
+        <f>INT((15-1)/4)+1</f>
         <v>4</v>
       </c>
-      <c r="C19" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A19)</f>
+      <c r="C19" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A19)</f>
         <v>3</v>
       </c>
-      <c r="D19" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A19,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <f aca="false">IF(C19=0,0,D19/C19)</f>
+      <c r="D19" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A19,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="21"/>
       <c r="H19" s="23"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="n">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="n">
-        <f aca="false">INT((16-1)/4)+1</f>
+      <c r="B20" s="18">
+        <f>INT((16-1)/4)+1</f>
         <v>4</v>
       </c>
-      <c r="C20" s="24" t="n">
-        <f aca="false">COUNTIF('Weekly Plan'!$C$5:$C$57,A20)</f>
+      <c r="C20" s="24">
+        <f>COUNTIF('Weekly Plan'!$C$5:$C$57,A20)</f>
         <v>3</v>
       </c>
-      <c r="D20" s="24" t="n">
-        <f aca="false">COUNTIFS('Weekly Plan'!$C$5:$C$57,A20,'Weekly Plan'!$G$5:$G$57,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="25" t="n">
-        <f aca="false">IF(C20=0,0,D20/C20)</f>
+      <c r="D20" s="24">
+        <f>COUNTIFS('Weekly Plan'!$C$5:$C$57,A20,'Weekly Plan'!$G$5:$G$57,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F20" s="26"/>
       <c r="G20" s="21"/>
       <c r="H20" s="23"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="27" t="n">
-        <f aca="false">SUM(C5:C20)</f>
+      <c r="C21" s="27">
+        <f>SUM(C5:C20)</f>
         <v>53</v>
       </c>
-      <c r="D21" s="27" t="n">
-        <f aca="false">SUM(D5:D20)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="28" t="n">
-        <f aca="false">IF(C21=0,0,D21/C21)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="29" t="n">
-        <f aca="false">SUM(F5:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="29" t="n">
-        <f aca="false">IF(COUNT(G5:G20)=0,0,AVERAGE(G5:G20))</f>
+      <c r="D21" s="27">
+        <f>SUM(D5:D20)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="29">
+        <f>SUM(F5:F20)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="29">
+        <f>IF(COUNT(G5:G20)=0,0,AVERAGE(G5:G20))</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G20" type="whole">
+    <dataValidation type="whole" allowBlank="1" sqref="G5:G20">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>108</v>
       </c>
@@ -4413,7 +4330,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>124</v>
       </c>
@@ -4434,7 +4351,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>129</v>
       </c>
@@ -4455,7 +4372,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>132</v>
       </c>
@@ -4476,7 +4393,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>136</v>
       </c>
@@ -4499,52 +4416,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E5:E8">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E8" type="list">
+    <dataValidation type="list" sqref="E5:E8">
       <formula1>"Not Started,Studying,Booked,Passed,Failed - Retake"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="48" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>143</v>
       </c>
@@ -4564,11 +4473,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="30">
         <v>46307</v>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="23">
         <v>1</v>
       </c>
       <c r="C5" s="23" t="s">
@@ -4580,11 +4489,11 @@
       <c r="E5" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="31">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="30"/>
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
@@ -4592,7 +4501,7 @@
       <c r="E6" s="23"/>
       <c r="F6" s="31"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="30"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
@@ -4600,7 +4509,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="31"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="30"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -4608,7 +4517,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="31"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="30"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
@@ -4616,7 +4525,7 @@
       <c r="E9" s="23"/>
       <c r="F9" s="31"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="30"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -4624,7 +4533,7 @@
       <c r="E10" s="23"/>
       <c r="F10" s="31"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -4632,7 +4541,7 @@
       <c r="E11" s="23"/>
       <c r="F11" s="31"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="30"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -4640,7 +4549,7 @@
       <c r="E12" s="23"/>
       <c r="F12" s="31"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -4648,7 +4557,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="31"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="30"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -4656,7 +4565,7 @@
       <c r="E14" s="23"/>
       <c r="F14" s="31"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="30"/>
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
@@ -4664,7 +4573,7 @@
       <c r="E15" s="23"/>
       <c r="F15" s="31"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="30"/>
       <c r="B16" s="23"/>
       <c r="C16" s="23"/>
@@ -4672,7 +4581,7 @@
       <c r="E16" s="23"/>
       <c r="F16" s="31"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="30"/>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
@@ -4680,7 +4589,7 @@
       <c r="E17" s="23"/>
       <c r="F17" s="31"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="30"/>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -4688,7 +4597,7 @@
       <c r="E18" s="23"/>
       <c r="F18" s="31"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="30"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
@@ -4696,7 +4605,7 @@
       <c r="E19" s="23"/>
       <c r="F19" s="31"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="30"/>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -4704,7 +4613,7 @@
       <c r="E20" s="23"/>
       <c r="F20" s="31"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="30"/>
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
@@ -4712,7 +4621,7 @@
       <c r="E21" s="23"/>
       <c r="F21" s="31"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="30"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
@@ -4720,7 +4629,7 @@
       <c r="E22" s="23"/>
       <c r="F22" s="31"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="30"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
@@ -4728,7 +4637,7 @@
       <c r="E23" s="23"/>
       <c r="F23" s="31"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="30"/>
       <c r="B24" s="23"/>
       <c r="C24" s="23"/>
@@ -4736,7 +4645,7 @@
       <c r="E24" s="23"/>
       <c r="F24" s="31"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="30"/>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
@@ -4744,7 +4653,7 @@
       <c r="E25" s="23"/>
       <c r="F25" s="31"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="30"/>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
@@ -4752,7 +4661,7 @@
       <c r="E26" s="23"/>
       <c r="F26" s="31"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="30"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
@@ -4760,7 +4669,7 @@
       <c r="E27" s="23"/>
       <c r="F27" s="31"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="30"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
@@ -4768,7 +4677,7 @@
       <c r="E28" s="23"/>
       <c r="F28" s="31"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="30"/>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
@@ -4776,7 +4685,7 @@
       <c r="E29" s="23"/>
       <c r="F29" s="31"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="30"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
@@ -4784,7 +4693,7 @@
       <c r="E30" s="23"/>
       <c r="F30" s="31"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="30"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
@@ -4792,7 +4701,7 @@
       <c r="E31" s="23"/>
       <c r="F31" s="31"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="30"/>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
@@ -4800,7 +4709,7 @@
       <c r="E32" s="23"/>
       <c r="F32" s="31"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="30"/>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
@@ -4808,7 +4717,7 @@
       <c r="E33" s="23"/>
       <c r="F33" s="31"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="30"/>
       <c r="B34" s="23"/>
       <c r="C34" s="23"/>
@@ -4816,7 +4725,7 @@
       <c r="E34" s="23"/>
       <c r="F34" s="31"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="30"/>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
@@ -4824,7 +4733,7 @@
       <c r="E35" s="23"/>
       <c r="F35" s="31"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="30"/>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -4832,7 +4741,7 @@
       <c r="E36" s="23"/>
       <c r="F36" s="31"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="30"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
@@ -4840,7 +4749,7 @@
       <c r="E37" s="23"/>
       <c r="F37" s="31"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="30"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
@@ -4848,7 +4757,7 @@
       <c r="E38" s="23"/>
       <c r="F38" s="31"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="30"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
@@ -4856,7 +4765,7 @@
       <c r="E39" s="23"/>
       <c r="F39" s="31"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="30"/>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -4864,7 +4773,7 @@
       <c r="E40" s="23"/>
       <c r="F40" s="31"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="30"/>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -4872,7 +4781,7 @@
       <c r="E41" s="23"/>
       <c r="F41" s="31"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="30"/>
       <c r="B42" s="23"/>
       <c r="C42" s="23"/>
@@ -4880,7 +4789,7 @@
       <c r="E42" s="23"/>
       <c r="F42" s="31"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="30"/>
       <c r="B43" s="23"/>
       <c r="C43" s="23"/>
@@ -4888,7 +4797,7 @@
       <c r="E43" s="23"/>
       <c r="F43" s="31"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="30"/>
       <c r="B44" s="23"/>
       <c r="C44" s="23"/>
@@ -4896,7 +4805,7 @@
       <c r="E44" s="23"/>
       <c r="F44" s="31"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="30"/>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
@@ -4904,7 +4813,7 @@
       <c r="E45" s="23"/>
       <c r="F45" s="31"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="30"/>
       <c r="B46" s="23"/>
       <c r="C46" s="23"/>
@@ -4912,7 +4821,7 @@
       <c r="E46" s="23"/>
       <c r="F46" s="31"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="30"/>
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
@@ -4920,7 +4829,7 @@
       <c r="E47" s="23"/>
       <c r="F47" s="31"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
@@ -4928,7 +4837,7 @@
       <c r="E48" s="23"/>
       <c r="F48" s="31"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="30"/>
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
@@ -4936,7 +4845,7 @@
       <c r="E49" s="23"/>
       <c r="F49" s="31"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="30"/>
       <c r="B50" s="23"/>
       <c r="C50" s="23"/>
@@ -4944,7 +4853,7 @@
       <c r="E50" s="23"/>
       <c r="F50" s="31"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="30"/>
       <c r="B51" s="23"/>
       <c r="C51" s="23"/>
@@ -4952,7 +4861,7 @@
       <c r="E51" s="23"/>
       <c r="F51" s="31"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="30"/>
       <c r="B52" s="23"/>
       <c r="C52" s="23"/>
@@ -4960,7 +4869,7 @@
       <c r="E52" s="23"/>
       <c r="F52" s="31"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="30"/>
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
@@ -4968,7 +4877,7 @@
       <c r="E53" s="23"/>
       <c r="F53" s="31"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="30"/>
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
@@ -4976,7 +4885,7 @@
       <c r="E54" s="23"/>
       <c r="F54" s="31"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="30"/>
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
@@ -4984,7 +4893,7 @@
       <c r="E55" s="23"/>
       <c r="F55" s="31"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="30"/>
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
@@ -4992,7 +4901,7 @@
       <c r="E56" s="23"/>
       <c r="F56" s="31"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="30"/>
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
@@ -5000,7 +4909,7 @@
       <c r="E57" s="23"/>
       <c r="F57" s="31"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="30"/>
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
@@ -5008,7 +4917,7 @@
       <c r="E58" s="23"/>
       <c r="F58" s="31"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="30"/>
       <c r="B59" s="23"/>
       <c r="C59" s="23"/>
@@ -5016,7 +4925,7 @@
       <c r="E59" s="23"/>
       <c r="F59" s="31"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="30"/>
       <c r="B60" s="23"/>
       <c r="C60" s="23"/>
@@ -5024,7 +4933,7 @@
       <c r="E60" s="23"/>
       <c r="F60" s="31"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="30"/>
       <c r="B61" s="23"/>
       <c r="C61" s="23"/>
@@ -5032,7 +4941,7 @@
       <c r="E61" s="23"/>
       <c r="F61" s="31"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="30"/>
       <c r="B62" s="23"/>
       <c r="C62" s="23"/>
@@ -5040,7 +4949,7 @@
       <c r="E62" s="23"/>
       <c r="F62" s="31"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="30"/>
       <c r="B63" s="23"/>
       <c r="C63" s="23"/>
@@ -5048,7 +4957,7 @@
       <c r="E63" s="23"/>
       <c r="F63" s="31"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="30"/>
       <c r="B64" s="23"/>
       <c r="C64" s="23"/>
@@ -5056,7 +4965,7 @@
       <c r="E64" s="23"/>
       <c r="F64" s="31"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="30"/>
       <c r="B65" s="23"/>
       <c r="C65" s="23"/>
@@ -5064,7 +4973,7 @@
       <c r="E65" s="23"/>
       <c r="F65" s="31"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="30"/>
       <c r="B66" s="23"/>
       <c r="C66" s="23"/>
@@ -5072,7 +4981,7 @@
       <c r="E66" s="23"/>
       <c r="F66" s="31"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="30"/>
       <c r="B67" s="23"/>
       <c r="C67" s="23"/>
@@ -5080,7 +4989,7 @@
       <c r="E67" s="23"/>
       <c r="F67" s="31"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="30"/>
       <c r="B68" s="23"/>
       <c r="C68" s="23"/>
@@ -5088,7 +4997,7 @@
       <c r="E68" s="23"/>
       <c r="F68" s="31"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="30"/>
       <c r="B69" s="23"/>
       <c r="C69" s="23"/>
@@ -5096,7 +5005,7 @@
       <c r="E69" s="23"/>
       <c r="F69" s="31"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="30"/>
       <c r="B70" s="23"/>
       <c r="C70" s="23"/>
@@ -5104,7 +5013,7 @@
       <c r="E70" s="23"/>
       <c r="F70" s="31"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="30"/>
       <c r="B71" s="23"/>
       <c r="C71" s="23"/>
@@ -5112,7 +5021,7 @@
       <c r="E71" s="23"/>
       <c r="F71" s="31"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="30"/>
       <c r="B72" s="23"/>
       <c r="C72" s="23"/>
@@ -5120,7 +5029,7 @@
       <c r="E72" s="23"/>
       <c r="F72" s="31"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="30"/>
       <c r="B73" s="23"/>
       <c r="C73" s="23"/>
@@ -5128,7 +5037,7 @@
       <c r="E73" s="23"/>
       <c r="F73" s="31"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="30"/>
       <c r="B74" s="23"/>
       <c r="C74" s="23"/>
@@ -5136,7 +5045,7 @@
       <c r="E74" s="23"/>
       <c r="F74" s="31"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="30"/>
       <c r="B75" s="23"/>
       <c r="C75" s="23"/>
@@ -5144,7 +5053,7 @@
       <c r="E75" s="23"/>
       <c r="F75" s="31"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="30"/>
       <c r="B76" s="23"/>
       <c r="C76" s="23"/>
@@ -5152,7 +5061,7 @@
       <c r="E76" s="23"/>
       <c r="F76" s="31"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="30"/>
       <c r="B77" s="23"/>
       <c r="C77" s="23"/>
@@ -5160,7 +5069,7 @@
       <c r="E77" s="23"/>
       <c r="F77" s="31"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="30"/>
       <c r="B78" s="23"/>
       <c r="C78" s="23"/>
@@ -5168,7 +5077,7 @@
       <c r="E78" s="23"/>
       <c r="F78" s="31"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="30"/>
       <c r="B79" s="23"/>
       <c r="C79" s="23"/>
@@ -5176,7 +5085,7 @@
       <c r="E79" s="23"/>
       <c r="F79" s="31"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="30"/>
       <c r="B80" s="23"/>
       <c r="C80" s="23"/>
@@ -5184,7 +5093,7 @@
       <c r="E80" s="23"/>
       <c r="F80" s="31"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="30"/>
       <c r="B81" s="23"/>
       <c r="C81" s="23"/>
@@ -5192,7 +5101,7 @@
       <c r="E81" s="23"/>
       <c r="F81" s="31"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="30"/>
       <c r="B82" s="23"/>
       <c r="C82" s="23"/>
@@ -5200,7 +5109,7 @@
       <c r="E82" s="23"/>
       <c r="F82" s="31"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="30"/>
       <c r="B83" s="23"/>
       <c r="C83" s="23"/>
@@ -5208,7 +5117,7 @@
       <c r="E83" s="23"/>
       <c r="F83" s="31"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="30"/>
       <c r="B84" s="23"/>
       <c r="C84" s="23"/>
@@ -5216,7 +5125,7 @@
       <c r="E84" s="23"/>
       <c r="F84" s="31"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="30"/>
       <c r="B85" s="23"/>
       <c r="C85" s="23"/>
@@ -5224,7 +5133,7 @@
       <c r="E85" s="23"/>
       <c r="F85" s="31"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="30"/>
       <c r="B86" s="23"/>
       <c r="C86" s="23"/>
@@ -5232,7 +5141,7 @@
       <c r="E86" s="23"/>
       <c r="F86" s="31"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="30"/>
       <c r="B87" s="23"/>
       <c r="C87" s="23"/>
@@ -5240,7 +5149,7 @@
       <c r="E87" s="23"/>
       <c r="F87" s="31"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="30"/>
       <c r="B88" s="23"/>
       <c r="C88" s="23"/>
@@ -5248,7 +5157,7 @@
       <c r="E88" s="23"/>
       <c r="F88" s="31"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="30"/>
       <c r="B89" s="23"/>
       <c r="C89" s="23"/>
@@ -5256,7 +5165,7 @@
       <c r="E89" s="23"/>
       <c r="F89" s="31"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="30"/>
       <c r="B90" s="23"/>
       <c r="C90" s="23"/>
@@ -5264,7 +5173,7 @@
       <c r="E90" s="23"/>
       <c r="F90" s="31"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="30"/>
       <c r="B91" s="23"/>
       <c r="C91" s="23"/>
@@ -5272,7 +5181,7 @@
       <c r="E91" s="23"/>
       <c r="F91" s="31"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="30"/>
       <c r="B92" s="23"/>
       <c r="C92" s="23"/>
@@ -5280,7 +5189,7 @@
       <c r="E92" s="23"/>
       <c r="F92" s="31"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="30"/>
       <c r="B93" s="23"/>
       <c r="C93" s="23"/>
@@ -5288,7 +5197,7 @@
       <c r="E93" s="23"/>
       <c r="F93" s="31"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="30"/>
       <c r="B94" s="23"/>
       <c r="C94" s="23"/>
@@ -5296,7 +5205,7 @@
       <c r="E94" s="23"/>
       <c r="F94" s="31"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="30"/>
       <c r="B95" s="23"/>
       <c r="C95" s="23"/>
@@ -5304,7 +5213,7 @@
       <c r="E95" s="23"/>
       <c r="F95" s="31"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="30"/>
       <c r="B96" s="23"/>
       <c r="C96" s="23"/>
@@ -5312,7 +5221,7 @@
       <c r="E96" s="23"/>
       <c r="F96" s="31"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="30"/>
       <c r="B97" s="23"/>
       <c r="C97" s="23"/>
@@ -5320,7 +5229,7 @@
       <c r="E97" s="23"/>
       <c r="F97" s="31"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="30"/>
       <c r="B98" s="23"/>
       <c r="C98" s="23"/>
@@ -5328,7 +5237,7 @@
       <c r="E98" s="23"/>
       <c r="F98" s="31"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="30"/>
       <c r="B99" s="23"/>
       <c r="C99" s="23"/>
@@ -5336,7 +5245,7 @@
       <c r="E99" s="23"/>
       <c r="F99" s="31"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="30"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23"/>
@@ -5344,7 +5253,7 @@
       <c r="E100" s="23"/>
       <c r="F100" s="31"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="30"/>
       <c r="B101" s="23"/>
       <c r="C101" s="23"/>
@@ -5352,7 +5261,7 @@
       <c r="E101" s="23"/>
       <c r="F101" s="31"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="30"/>
       <c r="B102" s="23"/>
       <c r="C102" s="23"/>
@@ -5360,7 +5269,7 @@
       <c r="E102" s="23"/>
       <c r="F102" s="31"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="30"/>
       <c r="B103" s="23"/>
       <c r="C103" s="23"/>
@@ -5368,7 +5277,7 @@
       <c r="E103" s="23"/>
       <c r="F103" s="31"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="30"/>
       <c r="B104" s="23"/>
       <c r="C104" s="23"/>
@@ -5376,7 +5285,7 @@
       <c r="E104" s="23"/>
       <c r="F104" s="31"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="30"/>
       <c r="B105" s="23"/>
       <c r="C105" s="23"/>
@@ -5385,12 +5294,7 @@
       <c r="F105" s="31"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>